--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -442,7 +442,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:13</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,33 +828,37 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,33 +1192,37 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
@@ -1435,22 +1467,22 @@
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>07:05</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1502,7 +1534,7 @@
       <c r="U9" s="2" t="inlineStr"/>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:05</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1538,35 +1570,35 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1604,7 +1636,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1836,7 +1868,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1875,46 +1907,50 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1952,7 +1988,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +2002,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2027,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2068,7 +2108,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2122,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2107,46 +2147,50 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2223,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2242,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2278,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2339,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2358,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,7 +2383,7 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
@@ -2350,35 +2394,35 @@
       <c r="AC16" s="2" t="inlineStr"/>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2455,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2474,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,18 +2499,22 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2527,7 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2489,7 +2537,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2527,12 +2575,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2594,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,35 +2630,35 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2643,12 +2691,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2662,7 +2710,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2698,35 +2746,35 @@
       <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2759,12 +2807,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2778,7 +2826,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2814,35 +2862,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/21</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2875,12 +2923,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2894,7 +2942,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2930,7 +2978,3275 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/3</t>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>07:37</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>77分钟</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>89分钟</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>2/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>1/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/9</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD49"/>
+  <dimension ref="A1:AD73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1149,24 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>07:48</t>
+          <t>07:46</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1217,12 +1225,12 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1603,32 +1635,36 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr"/>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1636,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1660,33 +1696,37 @@
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1759,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1752,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1820,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1916,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1988,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2027,7 +2075,7 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
@@ -2108,7 +2156,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2147,7 +2195,7 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
@@ -2228,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2344,7 +2392,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2388,13 +2436,17 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2512,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:22</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2509,40 +2561,40 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2575,12 +2627,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:04</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2594,7 +2646,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2619,46 +2671,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2696,7 +2752,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2710,7 +2766,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2735,46 +2791,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2812,7 +2872,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2826,7 +2886,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2851,46 +2911,50 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2923,12 +2987,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2942,7 +3006,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2967,46 +3031,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3044,7 +3112,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3058,7 +3126,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3083,46 +3151,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3160,7 +3232,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3174,7 +3246,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3199,46 +3271,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3271,12 +3347,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3290,7 +3366,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3315,18 +3391,22 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
@@ -3339,60 +3419,64 @@
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3406,7 +3490,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3416,33 +3500,37 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3455,60 +3543,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3522,7 +3614,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3532,33 +3624,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3571,60 +3667,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3638,7 +3738,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3648,17 +3748,17 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3668,13 +3768,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3791,7 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -3697,7 +3801,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -3735,12 +3839,12 @@
       <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3754,7 +3858,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3790,7 +3894,7 @@
       <c r="AC28" s="2" t="inlineStr"/>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3907,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3813,7 +3917,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3823,40 +3927,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3870,7 +3978,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3880,33 +3988,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3919,22 +4031,22 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3967,12 +4079,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3986,7 +4098,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4022,7 +4134,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4035,22 +4147,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4083,12 +4195,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4102,7 +4214,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4138,7 +4250,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4263,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4161,7 +4273,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4199,12 +4311,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4218,7 +4330,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4254,7 +4366,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4267,22 +4379,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4315,12 +4427,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4334,7 +4446,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4370,7 +4482,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4383,22 +4495,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4431,12 +4543,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4450,7 +4562,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4486,7 +4598,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4611,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4509,7 +4621,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4547,12 +4659,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4566,7 +4678,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4602,7 +4714,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4615,7 +4727,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4625,7 +4737,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4663,12 +4775,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4682,7 +4794,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4718,7 +4830,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4731,7 +4843,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4741,7 +4853,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4779,12 +4891,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4798,7 +4910,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4834,7 +4946,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4959,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -4857,7 +4969,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -4895,12 +5007,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4914,7 +5026,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4950,77 +5062,73 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/21</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>07:37</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5034,7 +5142,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5044,65 +5152,61 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5135,12 +5239,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5154,7 +5258,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5179,7 +5283,7 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
@@ -5190,35 +5294,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5251,12 +5355,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5270,7 +5374,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5306,77 +5410,73 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>08:29</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>89分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5390,7 +5490,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5400,17 +5500,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5420,45 +5520,41 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>89.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>2/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5491,12 +5587,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5510,7 +5606,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5546,35 +5642,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5607,12 +5703,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5626,7 +5722,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5662,35 +5758,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5723,12 +5819,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5742,7 +5838,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5778,35 +5874,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5839,12 +5935,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5858,7 +5954,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5883,50 +5979,46 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>1/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5959,12 +6051,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5978,7 +6070,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6014,35 +6106,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6075,12 +6167,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6094,7 +6186,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6130,35 +6222,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6191,12 +6283,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6210,7 +6302,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6235,7 +6327,7 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6246,7 +6338,2851 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>71分钟</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>08:07</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>1/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>4/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD73"/>
+  <dimension ref="A1:AD89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,17 +972,17 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1215,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1883,32 +1883,36 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1916,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1940,17 +1944,17 @@
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1960,17 +1964,17 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2003,32 +2007,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2036,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2060,17 +2068,17 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -2123,32 +2131,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2156,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2180,17 +2192,17 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2200,17 +2212,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
@@ -2243,32 +2255,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2276,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2300,33 +2316,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -2359,32 +2379,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2392,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2416,32 +2440,32 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2479,32 +2503,36 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2512,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2536,37 +2564,37 @@
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2660,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:04</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2671,7 +2699,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2752,7 +2780,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2872,7 +2900,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2911,7 +2939,7 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2926,7 +2954,7 @@
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2992,7 +3020,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3112,7 +3140,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3166,7 +3194,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>6/11</t>
+          <t>5/11</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3260,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3276,17 +3304,17 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>6/11</t>
         </is>
       </c>
     </row>
@@ -3299,22 +3327,22 @@
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>09:18</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3347,12 +3375,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3366,7 +3394,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3391,7 +3419,7 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3401,74 +3429,70 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>1/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3476,7 +3500,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3490,7 +3514,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3500,99 +3524,95 @@
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/11</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3600,7 +3620,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3614,7 +3634,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3624,99 +3644,95 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3724,7 +3740,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3738,7 +3754,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3748,65 +3764,65 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>1/11</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3844,7 +3860,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3858,7 +3874,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3883,88 +3899,88 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3978,7 +3994,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3988,22 +4004,22 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
@@ -4013,12 +4029,12 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4031,52 +4047,56 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>06:05</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4084,7 +4104,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4098,7 +4118,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4108,33 +4128,37 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4147,60 +4171,64 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4214,7 +4242,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4224,33 +4252,37 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4263,60 +4295,64 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4330,7 +4366,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4340,33 +4376,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4419,7 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -4389,7 +4429,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -4399,40 +4439,44 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4446,7 +4490,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4456,33 +4500,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4495,7 +4543,7 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -4505,7 +4553,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -4515,40 +4563,44 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4562,7 +4614,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4572,33 +4624,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -4611,60 +4667,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4678,7 +4738,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4688,33 +4748,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -4727,22 +4791,22 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4775,12 +4839,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4794,7 +4858,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4819,7 +4883,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4830,7 +4894,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4843,22 +4907,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4891,12 +4955,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4910,7 +4974,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4935,7 +4999,7 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4946,7 +5010,7 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4959,60 +5023,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5026,7 +5094,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5036,17 +5104,17 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5056,13 +5124,17 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5075,7 +5147,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5085,7 +5157,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5095,40 +5167,44 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5142,7 +5218,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5152,33 +5228,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5191,60 +5271,64 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5258,7 +5342,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5268,17 +5352,17 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5288,13 +5372,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5307,32 +5395,32 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -5355,12 +5443,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5368,13 +5456,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5410,7 +5514,7 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5527,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5433,7 +5537,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5471,12 +5575,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5490,7 +5594,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5526,7 +5630,7 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5539,7 +5643,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5549,7 +5653,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5587,12 +5691,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5606,7 +5710,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5642,7 +5746,7 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5655,32 +5759,32 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5703,12 +5807,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5716,13 +5820,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5758,7 +5874,7 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5771,7 +5887,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5781,7 +5897,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5819,12 +5935,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5838,7 +5954,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5874,7 +5990,7 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5887,22 +6003,22 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5935,7 +6051,7 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5954,7 +6070,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5990,7 +6106,7 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6003,7 +6119,7 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -6013,7 +6129,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -6056,7 +6172,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6070,7 +6186,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6106,7 +6222,7 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6235,7 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -6129,7 +6245,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -6167,12 +6283,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6186,7 +6302,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6222,7 +6338,7 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6235,7 +6351,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6245,7 +6361,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6283,12 +6399,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6302,7 +6418,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6338,7 +6454,7 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6467,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6361,7 +6477,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6399,12 +6515,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6418,7 +6534,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6454,7 +6570,7 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6467,22 +6583,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6520,7 +6636,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6534,7 +6650,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6570,7 +6686,7 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6583,22 +6699,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:38</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6631,12 +6747,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6650,7 +6766,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6675,22 +6791,18 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC52" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6703,22 +6815,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6751,12 +6863,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6770,7 +6882,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6795,22 +6907,18 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6823,22 +6931,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:48</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6871,12 +6979,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6890,7 +6998,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6926,7 +7034,7 @@
       <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -6939,22 +7047,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6992,7 +7100,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7006,7 +7114,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7031,92 +7139,84 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>134.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7130,7 +7230,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7140,65 +7240,61 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>71.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -7231,12 +7327,12 @@
       <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7250,7 +7346,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7280,83 +7376,83 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7370,7 +7466,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7380,17 +7476,17 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7405,82 +7501,78 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7494,7 +7586,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7504,65 +7596,61 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7595,12 +7683,12 @@
       <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7614,7 +7702,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7644,83 +7732,83 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7734,7 +7822,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7744,17 +7832,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7769,40 +7857,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7835,12 +7923,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7854,7 +7942,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7879,46 +7967,50 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7951,12 +8043,12 @@
       <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7970,7 +8062,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8005,40 +8097,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8071,12 +8163,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8090,7 +8182,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8115,7 +8207,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8126,35 +8218,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8187,12 +8279,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8206,7 +8298,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8231,7 +8323,7 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
@@ -8242,35 +8334,35 @@
       <c r="AC65" s="2" t="inlineStr"/>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8303,12 +8395,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8322,7 +8414,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8347,50 +8439,46 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8423,12 +8511,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8442,7 +8530,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8472,13 +8560,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -8491,60 +8583,64 @@
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8558,7 +8654,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8568,33 +8664,37 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -8607,22 +8707,22 @@
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8660,7 +8760,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8674,7 +8774,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8704,17 +8804,13 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -8727,52 +8823,56 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8780,7 +8880,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8794,7 +8894,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8804,17 +8904,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8824,13 +8924,17 @@
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8843,60 +8947,64 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8910,7 +9018,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8920,33 +9028,37 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB71" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8959,7 +9071,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8969,7 +9081,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8979,32 +9091,36 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9012,7 +9128,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9026,7 +9142,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9036,17 +9152,17 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9061,12 +9177,12 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>4/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9079,7 +9195,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9089,7 +9205,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9099,40 +9215,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9146,43 +9266,1959 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>94分钟</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>85分钟</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>87分钟</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>82分钟</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AC73" s="2" t="inlineStr"/>
-      <c r="AD73" s="2" t="inlineStr">
-        <is>
-          <t>—/12</t>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr"/>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr"/>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr"/>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr"/>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD89"/>
+  <dimension ref="A1:AD97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,17 +1468,17 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1592,17 +1592,17 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2627,32 +2627,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2684,17 +2688,17 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2704,17 +2708,17 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2747,32 +2751,36 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2780,7 +2788,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2804,17 +2812,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2824,17 +2832,17 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>10/11</t>
+          <t>8/11</t>
         </is>
       </c>
     </row>
@@ -2867,32 +2875,36 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2900,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2924,17 +2936,17 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2944,17 +2956,17 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3020,7 +3032,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3059,7 +3071,7 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3140,7 +3152,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3179,7 +3191,7 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
@@ -3194,7 +3206,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>5/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3272,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3380,7 +3392,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3500,7 +3512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3554,7 +3566,7 @@
       </c>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>2/11</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3632,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3674,7 +3686,7 @@
       </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>8/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3740,7 +3752,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3860,7 +3872,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3904,17 +3916,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/11</t>
+          <t>10/11</t>
         </is>
       </c>
     </row>
@@ -3980,7 +3992,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4024,79 +4036,75 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>08:09</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4118,7 +4126,7 @@
       <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4128,22 +4136,22 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4153,82 +4161,78 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4242,7 +4246,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4252,22 +4256,22 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4277,12 +4281,12 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>9/11</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4299,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4305,7 +4309,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4325,24 +4329,24 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>08:23</t>
+          <t>08:09</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -4352,7 +4356,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4366,7 +4370,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:18</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4401,12 +4405,12 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4419,24 +4423,24 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4449,12 +4453,12 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
@@ -4476,7 +4480,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4490,7 +4494,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4525,12 +4529,12 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4543,24 +4547,24 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:18</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:31</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4573,12 +4577,12 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
@@ -4600,7 +4604,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4614,7 +4618,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:18</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4649,12 +4653,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4667,24 +4671,24 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4697,24 +4701,24 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4724,7 +4728,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4738,7 +4742,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4773,12 +4777,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>124.0</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4791,60 +4795,64 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr"/>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4858,7 +4866,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4868,17 +4876,17 @@
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4888,13 +4896,17 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC36" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -4907,7 +4919,7 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -4917,7 +4929,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -4927,40 +4939,44 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4974,7 +4990,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4984,17 +5000,17 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5004,13 +5020,17 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5043,7 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -5033,7 +5053,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5043,44 +5063,40 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5094,7 +5110,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5104,37 +5120,33 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5159,7 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -5157,7 +5169,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5167,44 +5179,40 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>119分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5218,7 +5226,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5228,17 +5236,17 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5248,17 +5256,13 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5275,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5281,7 +5285,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5301,12 +5305,12 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
@@ -5323,12 +5327,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5342,7 +5346,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5367,22 +5371,22 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5395,7 +5399,7 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -5405,7 +5409,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5415,40 +5419,44 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq51，推进13站，达到≥2站确认条件</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5456,29 +5464,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>物理seq23（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5488,33 +5480,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>119.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -5527,7 +5523,7 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -5537,7 +5533,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5547,40 +5543,44 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr"/>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5624,13 +5624,17 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5647,7 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -5653,7 +5657,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -5663,12 +5667,12 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq55，推进17站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5691,12 +5695,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5704,13 +5708,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±3分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5759,32 +5779,32 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:24</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq47，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
@@ -5807,12 +5827,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5820,25 +5840,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>沪南路华夏西路</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
       <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
-        </is>
-      </c>
+      <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5887,7 +5895,7 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -5897,7 +5905,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -5907,40 +5915,44 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5954,7 +5966,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5964,33 +5976,37 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6003,32 +6019,32 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程31%处后消失；随后反向物理轨迹由seq39推进至seq55，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -6056,7 +6072,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6064,13 +6080,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>沪南路华夏西路</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq21映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -6119,22 +6147,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6167,12 +6195,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6186,7 +6214,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6235,22 +6263,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6283,12 +6311,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6302,7 +6330,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6351,7 +6379,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6361,7 +6389,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6399,12 +6427,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6418,7 +6446,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6467,7 +6495,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6477,7 +6505,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6515,12 +6543,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6534,7 +6562,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6583,22 +6611,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6631,12 +6659,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6650,7 +6678,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6699,22 +6727,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A57051D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6747,12 +6775,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6766,7 +6794,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6815,7 +6843,7 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -6825,7 +6853,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6863,12 +6891,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6882,7 +6910,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6931,7 +6959,7 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A57051D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -6941,7 +6969,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6979,12 +7007,12 @@
       <c r="N54" s="2" t="inlineStr"/>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6998,7 +7026,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -7047,7 +7075,7 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -7057,7 +7085,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -7095,12 +7123,12 @@
       <c r="N55" s="2" t="inlineStr"/>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7114,7 +7142,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7163,7 +7191,7 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -7173,7 +7201,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -7216,7 +7244,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7230,7 +7258,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7279,7 +7307,7 @@
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -7289,7 +7317,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7332,7 +7360,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7346,7 +7374,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7371,22 +7399,18 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>124.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7399,7 +7423,7 @@
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -7409,7 +7433,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7452,7 +7476,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7466,7 +7490,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7491,22 +7515,18 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC58" s="2" t="inlineStr">
-        <is>
-          <t>125.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7539,7 @@
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -7529,7 +7549,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7567,12 +7587,12 @@
       <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7586,7 +7606,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7611,18 +7631,22 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7635,22 +7659,22 @@
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7688,7 +7712,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7702,7 +7726,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7755,22 +7779,22 @@
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7803,12 +7827,12 @@
       <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7822,7 +7846,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7847,22 +7871,18 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>132.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr"/>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -7875,22 +7895,22 @@
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7928,7 +7948,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7942,7 +7962,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7977,12 +7997,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7995,22 +8015,22 @@
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A67057D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -8048,7 +8068,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8062,7 +8082,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -8097,12 +8117,12 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -8115,7 +8135,7 @@
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -8125,7 +8145,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -8163,12 +8183,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8182,7 +8202,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8212,13 +8232,17 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -8231,7 +8255,7 @@
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A67057D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -8241,7 +8265,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8279,12 +8303,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8298,7 +8322,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8328,13 +8352,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -8347,22 +8375,22 @@
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A79307D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>09:38</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8395,12 +8423,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8414,7 +8442,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8439,7 +8467,7 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
@@ -8463,22 +8491,22 @@
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8511,12 +8539,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8530,7 +8558,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8560,87 +8588,79 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>119.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8654,7 +8674,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8664,65 +8684,61 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8755,12 +8771,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8774,7 +8790,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8804,83 +8820,83 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>08:07</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8894,7 +8910,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8904,17 +8920,17 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8929,82 +8945,78 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9018,7 +9030,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -9028,17 +9040,17 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -9053,12 +9065,12 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -9071,7 +9083,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -9081,7 +9093,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -9101,24 +9113,24 @@
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9128,7 +9140,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9142,7 +9154,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9167,22 +9179,22 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9195,7 +9207,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9205,7 +9217,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9215,44 +9227,40 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9266,7 +9274,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9276,37 +9284,33 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr"/>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -9319,7 +9323,7 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -9329,7 +9333,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9349,19 +9353,19 @@
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9371,12 +9375,12 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9390,7 +9394,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>07:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9415,7 +9419,7 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
@@ -9425,12 +9429,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9447,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9453,7 +9457,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9473,12 +9477,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
@@ -9495,12 +9499,12 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9514,7 +9518,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>07:40</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9539,22 +9543,22 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9567,7 +9571,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9577,7 +9581,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9597,19 +9601,19 @@
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9619,12 +9623,12 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9638,7 +9642,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9663,22 +9667,22 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB76" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9691,7 +9695,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9701,7 +9705,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9721,34 +9725,34 @@
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9762,7 +9766,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9787,22 +9791,22 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB77" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9815,60 +9819,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9882,7 +9890,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9892,17 +9900,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9917,12 +9925,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9935,60 +9943,64 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10002,7 +10014,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>07:40</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -10012,33 +10024,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10051,60 +10067,64 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10118,7 +10138,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -10128,33 +10148,37 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB80" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10167,60 +10191,64 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10234,7 +10262,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10244,17 +10272,17 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10287,7 +10315,7 @@
       <c r="B82" s="2" t="inlineStr"/>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -10297,7 +10325,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -10340,7 +10368,7 @@
       </c>
       <c r="P82" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q82" s="2" t="inlineStr">
@@ -10354,7 +10382,7 @@
       <c r="U82" s="2" t="inlineStr"/>
       <c r="V82" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W82" s="2" t="inlineStr">
@@ -10379,7 +10407,7 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
@@ -10407,7 +10435,7 @@
       <c r="B83" s="2" t="inlineStr"/>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -10417,7 +10445,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -10455,12 +10483,12 @@
       <c r="N83" s="2" t="inlineStr"/>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10474,7 +10502,7 @@
       <c r="U83" s="2" t="inlineStr"/>
       <c r="V83" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W83" s="2" t="inlineStr">
@@ -10499,7 +10527,7 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
@@ -10523,22 +10551,22 @@
       <c r="B84" s="2" t="inlineStr"/>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
@@ -10571,12 +10599,12 @@
       <c r="N84" s="2" t="inlineStr"/>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10590,7 +10618,7 @@
       <c r="U84" s="2" t="inlineStr"/>
       <c r="V84" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W84" s="2" t="inlineStr">
@@ -10615,22 +10643,18 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC84" s="2" t="inlineStr">
-        <is>
-          <t>85.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr"/>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -10643,22 +10667,22 @@
       <c r="B85" s="2" t="inlineStr"/>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
@@ -10691,12 +10715,12 @@
       <c r="N85" s="2" t="inlineStr"/>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -10710,7 +10734,7 @@
       <c r="U85" s="2" t="inlineStr"/>
       <c r="V85" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W85" s="2" t="inlineStr">
@@ -10735,18 +10759,22 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB85" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10787,7 @@
       <c r="B86" s="2" t="inlineStr"/>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -10769,7 +10797,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -10807,12 +10835,12 @@
       <c r="N86" s="2" t="inlineStr"/>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -10826,7 +10854,7 @@
       <c r="U86" s="2" t="inlineStr"/>
       <c r="V86" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W86" s="2" t="inlineStr">
@@ -10851,18 +10879,22 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB86" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AD86" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10907,7 @@
       <c r="B87" s="2" t="inlineStr"/>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -10885,7 +10917,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10923,12 +10955,12 @@
       <c r="N87" s="2" t="inlineStr"/>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -10942,7 +10974,7 @@
       <c r="U87" s="2" t="inlineStr"/>
       <c r="V87" s="2" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W87" s="2" t="inlineStr">
@@ -10991,22 +11023,22 @@
       <c r="B88" s="2" t="inlineStr"/>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>09:20</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
@@ -11039,12 +11071,12 @@
       <c r="N88" s="2" t="inlineStr"/>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11058,7 +11090,7 @@
       <c r="U88" s="2" t="inlineStr"/>
       <c r="V88" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W88" s="2" t="inlineStr">
@@ -11093,12 +11125,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11111,22 +11143,22 @@
       <c r="B89" s="2" t="inlineStr"/>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
@@ -11159,7 +11191,7 @@
       <c r="N89" s="2" t="inlineStr"/>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11178,47 +11210,991 @@
       <c r="U89" s="2" t="inlineStr"/>
       <c r="V89" s="2" t="inlineStr">
         <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X93" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA93" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
+      <c r="AB93" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC89" s="2" t="inlineStr">
+      <c r="AC93" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="AD89" s="2" t="inlineStr">
+      <c r="AD93" s="2" t="inlineStr">
         <is>
           <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,12 +724,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2336,17 +2336,17 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3452,17 +3452,17 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD31" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4568,17 +4568,17 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD42" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6552,12 +6552,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD49" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6800,17 +6800,17 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD56" s="2" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7544,12 +7544,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7792,17 +7792,17 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD64" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9032,17 +9032,17 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9085,24 +9085,24 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>3/11</t>
+          <t>7/11</t>
         </is>
       </c>
     </row>
@@ -9209,12 +9209,12 @@
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9345,12 +9345,12 @@
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -9360,7 +9360,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9447,32 +9447,36 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9480,7 +9484,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9504,17 +9508,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9524,12 +9528,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
@@ -9567,32 +9571,36 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:17</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9600,7 +9608,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9624,17 +9632,17 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9644,12 +9652,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -9687,32 +9695,36 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9720,7 +9732,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9744,17 +9756,17 @@
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9764,17 +9776,17 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>7/11</t>
+          <t>4/11</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9852,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9889,7 +9901,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9960,7 +9972,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -10004,12 +10016,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
@@ -10138,7 +10150,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10344,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10386,7 +10398,7 @@
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -10510,7 +10522,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10646,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -10824,7 +10836,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10878,7 +10890,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -10998,7 +11010,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11204,7 @@
       </c>
       <c r="P87" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q87" s="2" t="inlineStr">
@@ -11236,12 +11248,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AD87" s="2" t="inlineStr">
@@ -11316,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11506,7 +11518,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -11696,7 +11708,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11816,7 +11828,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11952,7 +11964,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11996,17 +12008,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -12242,7 +12254,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12324,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12432,7 +12444,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12486,7 +12498,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12556,7 +12568,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12610,7 +12622,7 @@
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12692,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12729,12 +12741,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12816,7 @@
       </c>
       <c r="P100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q100" s="2" t="inlineStr">
@@ -12853,12 +12865,12 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12940,7 @@
       </c>
       <c r="P101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q101" s="2" t="inlineStr">
@@ -12982,7 +12994,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13188,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13220,17 +13232,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -13478,7 +13490,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -13672,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13726,7 +13738,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -13796,7 +13808,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13850,7 +13862,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -13974,7 +13986,7 @@
       </c>
       <c r="AD109" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -14222,7 +14234,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -14346,7 +14358,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14428,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14470,7 +14482,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14804,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14836,12 +14848,12 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
@@ -14916,7 +14928,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15036,7 +15048,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15284,7 +15296,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15328,17 +15340,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -15462,7 +15474,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -15532,7 +15544,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15656,7 +15668,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15710,7 +15722,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15792,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15834,7 +15846,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15916,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -15953,12 +15965,12 @@
       </c>
       <c r="AC125" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16040,7 @@
       </c>
       <c r="P126" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q126" s="2" t="inlineStr">
@@ -16082,7 +16094,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -16326,7 +16338,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -16396,7 +16408,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16450,7 +16462,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -16574,7 +16586,7 @@
       </c>
       <c r="AD130" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16710,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -16822,7 +16834,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -17202,7 +17214,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17408,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17574,7 +17586,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17656,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17688,17 +17700,17 @@
       </c>
       <c r="AB139" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -17768,7 +17780,7 @@
       </c>
       <c r="P140" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q140" s="2" t="inlineStr">
@@ -17817,12 +17829,12 @@
       </c>
       <c r="AC140" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17904,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17946,7 +17958,7 @@
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18082,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -18442,7 +18454,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18702,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -19070,7 +19082,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -19140,7 +19152,7 @@
       </c>
       <c r="P151" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q151" s="2" t="inlineStr">
@@ -19184,12 +19196,12 @@
       </c>
       <c r="AB151" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC151" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AD151" s="2" t="inlineStr">
@@ -19264,7 +19276,7 @@
       </c>
       <c r="P152" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q152" s="2" t="inlineStr">
@@ -19313,12 +19325,12 @@
       </c>
       <c r="AC152" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -19388,7 +19400,7 @@
       </c>
       <c r="P153" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q153" s="2" t="inlineStr">
@@ -19432,17 +19444,17 @@
       </c>
       <c r="AB153" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC153" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19512,7 +19524,7 @@
       </c>
       <c r="P154" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q154" s="2" t="inlineStr">
@@ -19636,7 +19648,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19756,7 +19768,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19880,7 +19892,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19934,7 +19946,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20016,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20058,7 +20070,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -20128,7 +20140,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20182,7 +20194,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -20252,7 +20264,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20306,7 +20318,7 @@
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -20430,7 +20442,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -20500,7 +20512,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -21174,7 +21186,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -21418,7 +21430,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -21620,7 +21632,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21674,7 +21686,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -21717,24 +21729,24 @@
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
       <c r="M172" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O172" s="2" t="inlineStr">
@@ -21744,7 +21756,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21793,12 +21805,12 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -21831,32 +21843,36 @@
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
       <c r="M173" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -21864,7 +21880,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21888,17 +21904,17 @@
       </c>
       <c r="X173" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y173" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z173" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA173" s="2" t="inlineStr">
@@ -21908,17 +21924,17 @@
       </c>
       <c r="AB173" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC173" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -21961,24 +21977,24 @@
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
       <c r="M174" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O174" s="2" t="inlineStr">
@@ -21988,7 +22004,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22037,12 +22053,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -22075,32 +22091,36 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
       <c r="M175" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -22108,7 +22128,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22132,17 +22152,17 @@
       </c>
       <c r="X175" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y175" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z175" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA175" s="2" t="inlineStr">
@@ -22152,12 +22172,12 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>119.2</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
@@ -22195,12 +22215,12 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I176" s="2" t="inlineStr">
@@ -22228,7 +22248,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22236,10 +22256,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R176" s="2" t="inlineStr"/>
-      <c r="S176" s="2" t="inlineStr"/>
-      <c r="T176" s="2" t="inlineStr"/>
-      <c r="U176" s="2" t="inlineStr"/>
+      <c r="R176" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S176" s="2" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="T176" s="2" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="U176" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V176" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -22282,7 +22318,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -22315,32 +22351,36 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
       <c r="M177" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N177" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22348,7 +22388,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22372,17 +22412,17 @@
       </c>
       <c r="X177" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y177" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z177" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA177" s="2" t="inlineStr">
@@ -22392,17 +22432,17 @@
       </c>
       <c r="AB177" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -22468,7 +22508,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22555,12 +22595,12 @@
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22588,18 +22628,34 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
+          <t>21:21</t>
+        </is>
+      </c>
+      <c r="Q179" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R179" s="2" t="inlineStr">
+        <is>
+          <t>迎春路长柳路</t>
+        </is>
+      </c>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
           <t>20:21</t>
         </is>
       </c>
-      <c r="Q179" s="2" t="inlineStr">
-        <is>
-          <t>SHMAAS</t>
-        </is>
-      </c>
-      <c r="R179" s="2" t="inlineStr"/>
-      <c r="S179" s="2" t="inlineStr"/>
-      <c r="T179" s="2" t="inlineStr"/>
-      <c r="U179" s="2" t="inlineStr"/>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V179" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -22642,7 +22698,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -22708,7 +22764,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22828,7 +22884,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22882,7 +22938,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -22948,7 +23004,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23068,7 +23124,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23122,7 +23178,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -23188,7 +23244,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23242,7 +23298,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -23308,7 +23364,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23428,7 +23484,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23482,7 +23538,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -23606,7 +23662,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -23974,7 +24030,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24526,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -24540,7 +24596,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24589,12 +24645,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -24664,7 +24720,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24708,17 +24764,17 @@
       </c>
       <c r="AB196" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -25202,7 +25258,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -25644,7 +25700,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25688,12 +25744,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25768,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25812,17 +25868,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -25892,7 +25948,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25936,17 +25992,17 @@
       </c>
       <c r="AB206" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -26194,7 +26250,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -26264,7 +26320,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26313,12 +26369,12 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26568,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26556,17 +26612,17 @@
       </c>
       <c r="AB211" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -26690,7 +26746,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -27256,7 +27312,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27300,12 +27356,12 @@
       </c>
       <c r="AB217" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27380,7 +27436,7 @@
       </c>
       <c r="P218" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q218" s="2" t="inlineStr">
@@ -27424,17 +27480,17 @@
       </c>
       <c r="AB218" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC218" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -27504,7 +27560,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27548,17 +27604,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27682,7 +27738,7 @@
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -27872,7 +27928,7 @@
       </c>
       <c r="P222" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q222" s="2" t="inlineStr">
@@ -27916,17 +27972,17 @@
       </c>
       <c r="AB222" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC222" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -28244,7 +28300,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28288,12 +28344,12 @@
       </c>
       <c r="AB225" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28492,7 +28548,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28536,17 +28592,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -28616,7 +28672,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28660,17 +28716,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -28864,7 +28920,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28908,12 +28964,12 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
@@ -29414,7 +29470,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -29484,7 +29540,7 @@
       </c>
       <c r="P235" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q235" s="2" t="inlineStr">
@@ -29528,17 +29584,17 @@
       </c>
       <c r="AB235" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC235" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -29608,7 +29664,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29657,12 +29713,12 @@
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -29732,7 +29788,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -29776,12 +29832,12 @@
       </c>
       <c r="AB237" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC237" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD237" s="2" t="inlineStr">
@@ -29856,7 +29912,7 @@
       </c>
       <c r="P238" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q238" s="2" t="inlineStr">
@@ -29900,17 +29956,17 @@
       </c>
       <c r="AB238" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC238" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -30352,7 +30408,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30396,12 +30452,12 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
@@ -30530,7 +30586,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -30724,7 +30780,7 @@
       </c>
       <c r="P245" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q245" s="2" t="inlineStr">
@@ -30773,12 +30829,12 @@
       </c>
       <c r="AC245" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD245" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -30972,7 +31028,7 @@
       </c>
       <c r="P247" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q247" s="2" t="inlineStr">
@@ -31016,17 +31072,17 @@
       </c>
       <c r="AB247" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC247" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD247" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -31096,7 +31152,7 @@
       </c>
       <c r="P248" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q248" s="2" t="inlineStr">
@@ -31140,17 +31196,17 @@
       </c>
       <c r="AB248" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC248" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -31220,7 +31276,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31264,17 +31320,17 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -31468,7 +31524,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -31512,12 +31568,12 @@
       </c>
       <c r="AB251" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC251" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD251" s="2" t="inlineStr">
@@ -31890,7 +31946,7 @@
       </c>
       <c r="AD254" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -31960,7 +32016,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32004,12 +32060,12 @@
       </c>
       <c r="AB255" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32510,7 +32566,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -32576,7 +32632,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32620,17 +32676,17 @@
       </c>
       <c r="AB260" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -32700,7 +32756,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32744,17 +32800,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -32824,7 +32880,7 @@
       </c>
       <c r="P262" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q262" s="2" t="inlineStr">
@@ -32873,12 +32929,12 @@
       </c>
       <c r="AC262" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -32948,7 +33004,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -32992,12 +33048,12 @@
       </c>
       <c r="AB263" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC263" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD263" s="2" t="inlineStr">
@@ -33192,7 +33248,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33236,17 +33292,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -33610,7 +33666,7 @@
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -33680,7 +33736,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33724,12 +33780,12 @@
       </c>
       <c r="AB269" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -34230,7 +34286,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34263,32 +34319,36 @@
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr"/>
       <c r="M274" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N274" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O274" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34296,7 +34356,7 @@
       </c>
       <c r="P274" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q274" s="2" t="inlineStr">
@@ -34320,17 +34380,17 @@
       </c>
       <c r="X274" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y274" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z274" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA274" s="2" t="inlineStr">
@@ -34340,17 +34400,17 @@
       </c>
       <c r="AB274" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC274" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -34590,7 +34650,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -34633,24 +34693,24 @@
       </c>
       <c r="I277" s="2" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr"/>
       <c r="M277" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N277" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O277" s="2" t="inlineStr">
@@ -34660,7 +34720,7 @@
       </c>
       <c r="P277" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="Q277" s="2" t="inlineStr">
@@ -34709,12 +34769,12 @@
       </c>
       <c r="AC277" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -34747,32 +34807,36 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr"/>
       <c r="M278" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N278" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O278" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -34780,7 +34844,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34804,17 +34868,17 @@
       </c>
       <c r="X278" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y278" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z278" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA278" s="2" t="inlineStr">
@@ -34824,17 +34888,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34867,32 +34931,36 @@
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr"/>
       <c r="M279" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N279" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O279" s="2" t="inlineStr">
         <is>
           <t>11:50</t>
@@ -34900,7 +34968,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -34924,17 +34992,17 @@
       </c>
       <c r="X279" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y279" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z279" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA279" s="2" t="inlineStr">
@@ -34944,12 +35012,12 @@
       </c>
       <c r="AB279" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC279" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD279" s="2" t="inlineStr">
@@ -34987,32 +35055,36 @@
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr"/>
       <c r="M280" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N280" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O280" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -35020,7 +35092,7 @@
       </c>
       <c r="P280" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q280" s="2" t="inlineStr">
@@ -35044,17 +35116,17 @@
       </c>
       <c r="X280" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y280" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z280" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA280" s="2" t="inlineStr">
@@ -35064,17 +35136,17 @@
       </c>
       <c r="AB280" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC280" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -35107,32 +35179,36 @@
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:53</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N281" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N281" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O281" s="2" t="inlineStr">
         <is>
           <t>08:20</t>
@@ -35140,7 +35216,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35164,17 +35240,17 @@
       </c>
       <c r="X281" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y281" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z281" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA281" s="2" t="inlineStr">
@@ -35184,12 +35260,12 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35260,7 +35336,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35304,17 +35380,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -35380,7 +35456,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35424,12 +35500,12 @@
       </c>
       <c r="AB283" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">

--- a/data/export/2026-10-03-operations.xlsx
+++ b/data/export/2026-10-03-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD15" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD20" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD33" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6428,7 +6428,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD51" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7376,7 +7376,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7420,7 +7420,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD59" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8412,7 +8412,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD69" s="2" t="inlineStr">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>21:39</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
@@ -9732,7 +9732,7 @@
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AD75" s="2" t="inlineStr">
@@ -9819,32 +9819,36 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9852,7 +9856,7 @@
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9876,17 +9880,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9896,12 +9900,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AD76" s="2" t="inlineStr">
@@ -9939,32 +9943,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:25</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9972,7 +9980,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9996,17 +10004,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -10016,7 +10024,7 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -10150,7 +10158,7 @@
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -10274,7 +10282,7 @@
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -10344,7 +10352,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10388,17 +10396,17 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10530,7 @@
       </c>
       <c r="AD81" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10844,7 @@
       </c>
       <c r="P84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q84" s="2" t="inlineStr">
@@ -10880,17 +10888,17 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -11010,7 +11018,7 @@
       </c>
       <c r="AD85" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11336,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11372,7 +11380,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11518,7 +11526,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11646,7 @@
       </c>
       <c r="AD90" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11770,7 @@
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -12254,7 +12262,7 @@
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -12324,7 +12332,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12368,17 +12376,17 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -12444,7 +12452,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12498,7 +12506,7 @@
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12568,7 +12576,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12612,17 +12620,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -12746,7 +12754,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -12870,7 +12878,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -12994,7 +13002,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -13242,7 +13250,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13498,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13622,7 @@
       </c>
       <c r="AD106" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13692,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13738,7 +13746,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -13808,7 +13816,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13852,17 +13860,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -14234,7 +14242,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14366,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -14428,7 +14436,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14472,17 +14480,17 @@
       </c>
       <c r="AB113" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -14928,7 +14936,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14972,7 +14980,7 @@
       </c>
       <c r="AB117" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC117" s="2" t="inlineStr">
@@ -15102,7 +15110,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -15226,7 +15234,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -15474,7 +15482,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15552,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15588,17 +15596,17 @@
       </c>
       <c r="AB122" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC122" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15676,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15722,7 +15730,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -15792,7 +15800,7 @@
       </c>
       <c r="P124" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q124" s="2" t="inlineStr">
@@ -15836,17 +15844,17 @@
       </c>
       <c r="AB124" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC124" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -15970,7 +15978,7 @@
       </c>
       <c r="AD125" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -16094,7 +16102,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16346,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16416,7 @@
       </c>
       <c r="P129" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q129" s="2" t="inlineStr">
@@ -16462,7 +16470,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -16710,7 +16718,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16842,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -17214,7 +17222,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -17338,7 +17346,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -17586,7 +17594,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -17834,7 +17842,7 @@
       </c>
       <c r="AD140" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17912,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17948,17 +17956,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -18082,7 +18090,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18586,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -18702,7 +18710,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19082,7 +19090,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19338,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -19454,7 +19462,7 @@
       </c>
       <c r="AD153" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19586,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -19768,7 +19776,7 @@
       </c>
       <c r="P156" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q156" s="2" t="inlineStr">
@@ -19812,17 +19820,17 @@
       </c>
       <c r="AB156" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC156" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -19892,7 +19900,7 @@
       </c>
       <c r="P157" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q157" s="2" t="inlineStr">
@@ -19936,17 +19944,17 @@
       </c>
       <c r="AB157" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC157" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -20070,7 +20078,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -20140,7 +20148,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20194,7 +20202,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20272,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20308,17 +20316,17 @@
       </c>
       <c r="AB160" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -20442,7 +20450,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -20512,7 +20520,7 @@
       </c>
       <c r="P162" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q162" s="2" t="inlineStr">
@@ -20556,7 +20564,7 @@
       </c>
       <c r="AB162" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC162" s="2" t="inlineStr">
@@ -20938,7 +20946,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -21062,7 +21070,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -21186,7 +21194,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -21430,7 +21438,7 @@
       </c>
       <c r="AD169" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -21632,7 +21640,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21686,7 +21694,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -21810,7 +21818,7 @@
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22066,7 @@
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -22318,7 +22326,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -22442,7 +22450,7 @@
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -22562,7 +22570,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -22600,7 +22608,7 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq56，推进28站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I179" s="2" t="inlineStr">
@@ -22628,7 +22636,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22698,7 +22706,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -22851,32 +22859,36 @@
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
       <c r="M181" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N181" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -22884,7 +22896,7 @@
       </c>
       <c r="P181" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q181" s="2" t="inlineStr">
@@ -22908,17 +22920,17 @@
       </c>
       <c r="X181" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y181" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z181" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA181" s="2" t="inlineStr">
@@ -22928,17 +22940,17 @@
       </c>
       <c r="AB181" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC181" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -22971,32 +22983,36 @@
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:47</t>
         </is>
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
       <c r="M182" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N182" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -23004,7 +23020,7 @@
       </c>
       <c r="P182" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q182" s="2" t="inlineStr">
@@ -23028,17 +23044,17 @@
       </c>
       <c r="X182" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y182" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z182" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA182" s="2" t="inlineStr">
@@ -23048,17 +23064,17 @@
       </c>
       <c r="AB182" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC182" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -23091,32 +23107,36 @@
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
       <c r="M183" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N183" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -23124,7 +23144,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23148,17 +23168,17 @@
       </c>
       <c r="X183" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y183" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z183" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA183" s="2" t="inlineStr">
@@ -23168,17 +23188,17 @@
       </c>
       <c r="AB183" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>127.2</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -23211,32 +23231,36 @@
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>115分钟</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
       <c r="M184" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N184" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -23244,7 +23268,7 @@
       </c>
       <c r="P184" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q184" s="2" t="inlineStr">
@@ -23268,17 +23292,17 @@
       </c>
       <c r="X184" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y184" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z184" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA184" s="2" t="inlineStr">
@@ -23288,17 +23312,17 @@
       </c>
       <c r="AB184" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC184" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -23331,32 +23355,36 @@
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:42</t>
         </is>
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
       <c r="M185" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N185" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -23364,7 +23392,7 @@
       </c>
       <c r="P185" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q185" s="2" t="inlineStr">
@@ -23388,17 +23416,17 @@
       </c>
       <c r="X185" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y185" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z185" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA185" s="2" t="inlineStr">
@@ -23408,7 +23436,7 @@
       </c>
       <c r="AB185" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC185" s="2" t="inlineStr">
@@ -23484,7 +23512,7 @@
       </c>
       <c r="P186" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>22:41</t>
         </is>
       </c>
       <c r="Q186" s="2" t="inlineStr">
@@ -23538,7 +23566,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -24030,7 +24058,7 @@
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -25258,7 +25286,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -25700,7 +25728,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25749,7 +25777,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25824,7 +25852,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25868,17 +25896,17 @@
       </c>
       <c r="AB205" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -26746,7 +26774,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -27312,7 +27340,7 @@
       </c>
       <c r="P217" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q217" s="2" t="inlineStr">
@@ -27361,7 +27389,7 @@
       </c>
       <c r="AC217" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD217" s="2" t="inlineStr">
@@ -27560,7 +27588,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27604,17 +27632,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28300,7 +28328,7 @@
       </c>
       <c r="P225" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q225" s="2" t="inlineStr">
@@ -28349,7 +28377,7 @@
       </c>
       <c r="AC225" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD225" s="2" t="inlineStr">
@@ -28548,7 +28576,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28592,17 +28620,17 @@
       </c>
       <c r="AB227" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -28920,7 +28948,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -29470,7 +29498,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -29788,7 +29816,7 @@
       </c>
       <c r="P237" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q237" s="2" t="inlineStr">
@@ -30408,7 +30436,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30457,7 +30485,7 @@
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
@@ -30586,7 +30614,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -31276,7 +31304,7 @@
       </c>
       <c r="P249" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q249" s="2" t="inlineStr">
@@ -31320,17 +31348,17 @@
       </c>
       <c r="AB249" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC249" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -31524,7 +31552,7 @@
       </c>
       <c r="P251" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q251" s="2" t="inlineStr">
@@ -32016,7 +32044,7 @@
       </c>
       <c r="P255" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q255" s="2" t="inlineStr">
@@ -32065,7 +32093,7 @@
       </c>
       <c r="AC255" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD255" s="2" t="inlineStr">
@@ -32566,7 +32594,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -32756,7 +32784,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32800,17 +32828,17 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -33004,7 +33032,7 @@
       </c>
       <c r="P263" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q263" s="2" t="inlineStr">
@@ -33736,7 +33764,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33785,7 +33813,7 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -34286,7 +34314,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -34844,7 +34872,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34888,17 +34916,17 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -34968,7 +34996,7 @@
       </c>
       <c r="P279" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q279" s="2" t="inlineStr">
@@ -35189,24 +35217,24 @@
       </c>
       <c r="I281" s="2" t="inlineStr">
         <is>
-          <t>21:53</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr"/>
       <c r="M281" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N281" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O281" s="2" t="inlineStr">
@@ -35216,7 +35244,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35265,7 +35293,7 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35303,32 +35331,36 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr"/>
       <c r="M282" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N282" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N282" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O282" s="2" t="inlineStr">
         <is>
           <t>08:40</t>
@@ -35336,7 +35368,7 @@
       </c>
       <c r="P282" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q282" s="2" t="inlineStr">
@@ -35360,17 +35392,17 @@
       </c>
       <c r="X282" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y282" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z282" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA282" s="2" t="inlineStr">
@@ -35380,17 +35412,17 @@
       </c>
       <c r="AB282" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC282" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AD282" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -35456,7 +35488,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
